--- a/src/main/resources/espacios/1 Step/0 - Preguntas Simples Fluidez.xlsx
+++ b/src/main/resources/espacios/1 Step/0 - Preguntas Simples Fluidez.xlsx
@@ -5,14 +5,13 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="1 Fluidez" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="2 Fluidez" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="3 Fluidez" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="4 Fluidez" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="5 Fluidez" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -24,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6297" uniqueCount="4665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6285" uniqueCount="4653">
   <si>
     <t xml:space="preserve">How's it going?</t>
   </si>
@@ -13983,42 +13982,6 @@
   </si>
   <si>
     <t xml:space="preserve">jɛs, ɪts ˈʌndər ðə neɪm smɪθ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Can you ask if the feature is ready for testing?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check if the API integration is ready for review.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Could you confirm if the bug fix is ready to deploy?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Can you ask if the front-end changes are ready to be merged?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Is the database configuration ready for the next environment?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Can you check if the documentation is ready for the new module?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Can someone ask the DevOps team if the environment is ready?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Do we know if the data for the report is ready?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Could you check if the test cases are ready for automation?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ask if the user stories are ready for the next sprint.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Can we confirm if the release notes are ready?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Is the demo environment ready for the review?</t>
   </si>
 </sst>
 </file>
@@ -14099,7 +14062,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -14109,10 +14072,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -36388,87 +36347,4 @@
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:A12"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="60.05"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="3" width="11.53"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>4653</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>4654</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>4655</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>4656</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>4657</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>4658</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>4659</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>4660</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>4661</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>4662</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>4663</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>4664</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>